--- a/GUA/Modelos/Residuos/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
+++ b/GUA/Modelos/Residuos/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\Desktop\GUA_Modelos_SectorialesV2\M1_Waste\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClimateLeadGroup\Desktop\CLG_repositories\openmodels_lac\GUA\Modelos\Residuos\A2_Extra_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BB1B27-17DB-4E66-B8E9-A67247E69796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7869BC05-BBDE-4008-8FC3-F47C74E31CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Other_Params" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>All</t>
-  </si>
-  <si>
-    <t>NDP</t>
   </si>
 </sst>
 </file>
@@ -547,7 +544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -574,9 +571,7 @@
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>10</v>
-      </c>
+      <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -609,12 +604,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -841,27 +837,47 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EF093B-66D8-481C-9675-90EBD4EEB36E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E051536C-7B99-4C3A-887E-8FAA0EACB30C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A75D7A-0551-486B-B9F6-37F32AA206F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E051536C-7B99-4C3A-887E-8FAA0EACB30C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EF093B-66D8-481C-9675-90EBD4EEB36E}"/>
 </file>